--- a/sharedata/excel/G-功能解锁表(FeatureData).xlsx
+++ b/sharedata/excel/G-功能解锁表(FeatureData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,8 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="功能解锁表(FeatureData)" sheetId="1" r:id="rId1"/>
-    <sheet name="#神器待配置" sheetId="2" r:id="rId2"/>
-    <sheet name="#集市待配置" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>功能解锁表</t>
   </si>
@@ -132,115 +130,79 @@
     <t>装备分解</t>
   </si>
   <si>
-    <t>已确认逻辑入口，正式编号与门槛尚待配置；本页以#开头，不参与导表。</t>
-  </si>
-  <si>
-    <t>功能检索名</t>
-  </si>
-  <si>
-    <t>功能用途</t>
-  </si>
-  <si>
-    <t>正式编号</t>
-  </si>
-  <si>
-    <t>门槛与提示</t>
-  </si>
-  <si>
-    <t>神器</t>
-  </si>
-  <si>
-    <t>神器图鉴、激活、穿戴及培养的总入口</t>
-  </si>
-  <si>
-    <t>待配置</t>
-  </si>
-  <si>
-    <t>创角、开服、VIP、主线、建筑条件及锁定提示待配置</t>
-  </si>
-  <si>
-    <t>神器转移</t>
-  </si>
-  <si>
-    <t>神器强化经验转移入口</t>
-  </si>
-  <si>
-    <t>独立解锁门槛及锁定提示待配置</t>
-  </si>
-  <si>
-    <t>神器重置</t>
-  </si>
-  <si>
-    <t>神器强化经验重置入口</t>
-  </si>
-  <si>
-    <t>集市功能解锁待配置（本页不参与导表）</t>
-  </si>
-  <si>
-    <t>计划检索名</t>
-  </si>
-  <si>
-    <t>待配置内容</t>
-  </si>
-  <si>
-    <t>规则</t>
-  </si>
-  <si>
-    <t>集市入口及每日商店</t>
+    <t>Council</t>
+  </si>
+  <si>
+    <t>议事厅</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_议事厅</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>兵营</t>
+  </si>
+  <si>
+    <t>议事厅-1级</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_兵营</t>
+  </si>
+  <si>
+    <t>MagicTower</t>
+  </si>
+  <si>
+    <t>魔法塔</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_魔法塔</t>
+  </si>
+  <si>
+    <t>Tavern</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_酒馆</t>
+  </si>
+  <si>
+    <t>TavernDraw</t>
+  </si>
+  <si>
+    <t>英雄召唤</t>
+  </si>
+  <si>
+    <t>酒馆-1级</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_英雄召唤</t>
+  </si>
+  <si>
+    <t>MarketDaily</t>
   </si>
   <si>
     <t>每日商店</t>
   </si>
   <si>
-    <t>正式编号、适用门槛、锁定提示</t>
-  </si>
-  <si>
-    <t>入口共用每日商店feature_id，不额外建立独立入口条件</t>
-  </si>
-  <si>
-    <t>资源商店分页</t>
+    <t>集市-1级</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_每日商店</t>
+  </si>
+  <si>
+    <t>MarketResource</t>
   </si>
   <si>
     <t>资源商店</t>
   </si>
   <si>
-    <t>未解锁隐藏，解锁后加入页签并生成当前周期库存</t>
-  </si>
-  <si>
-    <t>可选栏位门槛</t>
-  </si>
-  <si>
-    <t>待确定实际栏位后命名</t>
-  </si>
-  <si>
-    <t>需要独立功能条件的栏位才配FeatureData</t>
-  </si>
-  <si>
-    <t>feature_id与unlock_level都填时同时满足；都空时随分页</t>
-  </si>
-  <si>
-    <t>关卡依赖</t>
-  </si>
-  <si>
-    <t>StageData尚未建立</t>
-  </si>
-  <si>
-    <t>选用主线条件时须有真实关卡记录</t>
-  </si>
-  <si>
-    <t>不填旧项目关卡或0代替未定条件；无需主线条件时不造关卡</t>
-  </si>
-  <si>
-    <t>发布要求</t>
-  </si>
-  <si>
-    <t>本页无有效功能记录</t>
-  </si>
-  <si>
-    <t>待规则与编号确定后迁入FeatureData正式页</t>
-  </si>
-  <si>
-    <t>不得复制待配置占位主键或将空门槛当成自动开放</t>
+    <t>集市-2级</t>
+  </si>
+  <si>
+    <t>$Lang$临时解锁提示_资源商店</t>
   </si>
 </sst>
 </file>
@@ -268,13 +230,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -429,15 +398,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,12 +414,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6C6AD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -643,7 +599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -663,21 +619,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -784,194 +725,176 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1445,516 +1368,306 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.1111111111111" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="8" customWidth="1"/>
-    <col min="3" max="3" width="7.88888888888889" style="8" customWidth="1"/>
-    <col min="4" max="4" width="10.8888888888889" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.7777777777778" style="8" customWidth="1"/>
-    <col min="6" max="6" width="7.44444444444444" style="8" customWidth="1"/>
-    <col min="7" max="7" width="13.2222222222222" style="8" customWidth="1"/>
-    <col min="8" max="8" width="17.1111111111111" style="8" customWidth="1"/>
-    <col min="9" max="9" width="9.55555555555556" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="8" customWidth="1"/>
+    <col min="1" max="1" width="11.1111111111111" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="3" customWidth="1"/>
+    <col min="3" max="3" width="7.88888888888889" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.8888888888889" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.44444444444444" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.1111111111111" style="3" customWidth="1"/>
+    <col min="9" max="9" width="26.3333333333333" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:9">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="7" customFormat="1" spans="1:9">
-      <c r="A4" s="10" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:9">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" spans="1:9">
-      <c r="A5" s="10" t="s">
+    <row r="5" s="2" customFormat="1" spans="1:9">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="7" customFormat="1" spans="1:9">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="2" customFormat="1" spans="1:9">
+      <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
-    <row r="9" ht="66.0" customHeight="1">
-      <c r="B9" t="str" s="12">
-        <v>Council</v>
-      </c>
-      <c r="C9" t="str" s="12">
-        <v>议事厅</v>
-      </c>
-      <c r="D9" t="n" s="12">
+    <row r="9" spans="1:9">
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="7">
         <v>0</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" t="str" s="13">
-        <v>$Lang$临时解锁提示_议事厅</v>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="10" ht="66.0" customHeight="1">
-      <c r="B10" t="str" s="12">
-        <v>Barracks</v>
-      </c>
-      <c r="C10" t="str" s="12">
-        <v>兵营</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" t="str" s="12">
-        <v>议事厅-1级</v>
-      </c>
-      <c r="I10" t="str" s="13">
-        <v>$Lang$临时解锁提示_兵营</v>
+    <row r="10" spans="1:9">
+      <c r="B10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="11" ht="66.0" customHeight="1">
-      <c r="B11" t="str" s="12">
-        <v>MagicTower</v>
-      </c>
-      <c r="C11" t="str" s="12">
-        <v>魔法塔</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" t="str" s="12">
-        <v>议事厅-1级</v>
-      </c>
-      <c r="I11" t="str" s="13">
-        <v>$Lang$临时解锁提示_魔法塔</v>
+    <row r="11" spans="1:9">
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="12" ht="66.0" customHeight="1">
-      <c r="B12" t="str" s="12">
-        <v>Tavern</v>
-      </c>
-      <c r="C12" t="str" s="12">
-        <v>酒馆</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" t="str" s="12">
-        <v>议事厅-1级</v>
-      </c>
-      <c r="I12" t="str" s="13">
-        <v>$Lang$临时解锁提示_酒馆</v>
+    <row r="12" spans="1:9">
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="13" ht="66.0" customHeight="1">
-      <c r="B13" t="str" s="12">
-        <v>TavernDraw</v>
-      </c>
-      <c r="C13" t="str" s="13">
-        <v>英雄召唤</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" t="str" s="12">
-        <v>酒馆-1级</v>
-      </c>
-      <c r="I13" t="str" s="13">
-        <v>$Lang$临时解锁提示_英雄召唤</v>
+    <row r="13" spans="1:9">
+      <c r="B13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="14" ht="66.0" customHeight="1">
-      <c r="B14" t="str" s="12">
-        <v>MarketDaily</v>
-      </c>
-      <c r="C14" t="str" s="13">
-        <v>每日商店</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" t="str" s="12">
-        <v>集市-1级</v>
-      </c>
-      <c r="I14" t="str" s="13">
-        <v>$Lang$临时解锁提示_每日商店</v>
+    <row r="14" spans="1:9">
+      <c r="B14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="15" ht="66.0" customHeight="1">
-      <c r="B15" t="str" s="13">
-        <v>MarketResource</v>
-      </c>
-      <c r="C15" t="str" s="13">
-        <v>资源商店</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" t="str" s="12">
-        <v>集市-2级</v>
-      </c>
-      <c r="I15" t="str" s="13">
-        <v>$Lang$临时解锁提示_资源商店</v>
+    <row r="15" spans="1:9">
+      <c r="B15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:4">
-      <c r="A1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:4">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="73" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" ht="33" customHeight="1" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>